--- a/data/trans_orig/P2C_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P2C_R-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28991</t>
+          <t>29319</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40653</t>
+          <t>40755</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>51,35%</t>
+          <t>51,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>72,0%</t>
+          <t>72,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27128</t>
+          <t>27796</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38100</t>
+          <t>38119</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,81%</t>
+          <t>54,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>74,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>60592</t>
+          <t>59499</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>75746</t>
+          <t>75975</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>56,19%</t>
+          <t>55,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,24%</t>
+          <t>70,46%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15809</t>
+          <t>15707</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27471</t>
+          <t>27143</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,65%</t>
+          <t>48,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13271</t>
+          <t>13252</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24243</t>
+          <t>23575</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>32087</t>
+          <t>31858</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>47241</t>
+          <t>48334</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>44,82%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>195215</t>
+          <t>195061</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>221347</t>
+          <t>223139</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>62,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>71,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>228108</t>
+          <t>227569</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>256178</t>
+          <t>255192</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>64,5%</t>
+          <t>64,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>72,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>432263</t>
+          <t>432589</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>467828</t>
+          <t>469943</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>65,1%</t>
+          <t>65,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>70,78%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>88970</t>
+          <t>87178</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>115102</t>
+          <t>115256</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>97458</t>
+          <t>98444</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>125528</t>
+          <t>126067</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>35,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>196125</t>
+          <t>194010</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>231690</t>
+          <t>231364</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>34,85%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>98178</t>
+          <t>98249</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>113720</t>
+          <t>113989</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>83,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>80648</t>
+          <t>80473</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>96860</t>
+          <t>97282</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>65,28%</t>
+          <t>65,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>78,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>183100</t>
+          <t>183495</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>205643</t>
+          <t>206613</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>70,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>79,43%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22861</t>
+          <t>22592</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>38403</t>
+          <t>38332</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26682</t>
+          <t>26260</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>42894</t>
+          <t>43069</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>54480</t>
+          <t>53510</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>77023</t>
+          <t>76628</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,46%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>333400</t>
+          <t>334656</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>366650</t>
+          <t>367316</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>66,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>72,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>346609</t>
+          <t>346730</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>381488</t>
+          <t>380608</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>65,58%</t>
+          <t>65,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>72,18%</t>
+          <t>72,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>691673</t>
+          <t>689538</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>741191</t>
+          <t>738597</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>67,03%</t>
+          <t>66,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>71,58%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>136709</t>
+          <t>136043</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>169959</t>
+          <t>168703</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>147061</t>
+          <t>147941</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>181940</t>
+          <t>181819</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>290717</t>
+          <t>293311</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>340235</t>
+          <t>342370</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>33,18%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>42715</t>
+          <t>42741</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51507</t>
+          <t>51472</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>77,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>48521</t>
+          <t>48848</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57372</t>
+          <t>57583</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>78,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>94601</t>
+          <t>94912</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>106909</t>
+          <t>107615</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>91,53%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3977</t>
+          <t>4012</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12769</t>
+          <t>12743</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4718</t>
+          <t>4507</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13569</t>
+          <t>13242</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10665</t>
+          <t>9959</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>22973</t>
+          <t>22662</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,27%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>262076</t>
+          <t>262695</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>279418</t>
+          <t>279880</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>280504</t>
+          <t>280295</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>301202</t>
+          <t>301359</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>547981</t>
+          <t>550182</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>576275</t>
+          <t>576720</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,49%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>25235</t>
+          <t>24773</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>42577</t>
+          <t>41958</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>38591</t>
+          <t>38434</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>59289</t>
+          <t>59498</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>68171</t>
+          <t>67726</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>96465</t>
+          <t>94264</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,63%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>104039</t>
+          <t>104652</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>112860</t>
+          <t>113071</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>122619</t>
+          <t>123058</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>132186</t>
+          <t>131854</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>230471</t>
+          <t>230908</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>243303</t>
+          <t>243142</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,83%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3967</t>
+          <t>3756</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12788</t>
+          <t>12175</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4712</t>
+          <t>5044</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14279</t>
+          <t>13840</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>10422</t>
+          <t>10583</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>23254</t>
+          <t>22817</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>8,99%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>417091</t>
+          <t>418324</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>439171</t>
+          <t>438557</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>459598</t>
+          <t>461494</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>485395</t>
+          <t>486339</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>884960</t>
+          <t>884572</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>917749</t>
+          <t>918467</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,42%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>37794</t>
+          <t>38408</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>59874</t>
+          <t>58641</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>53386</t>
+          <t>52442</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>79183</t>
+          <t>77287</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>97997</t>
+          <t>97279</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>130786</t>
+          <t>131174</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,91%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26487</t>
+          <t>26105</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34878</t>
+          <t>34829</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>65,17%</t>
+          <t>64,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33365</t>
+          <t>32882</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42841</t>
+          <t>43438</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>65,12%</t>
+          <t>64,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>84,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>63127</t>
+          <t>62262</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>76334</t>
+          <t>76064</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>68,71%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>82,79%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5763</t>
+          <t>5812</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14154</t>
+          <t>14536</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8396</t>
+          <t>7799</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17872</t>
+          <t>18355</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15544</t>
+          <t>15814</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28751</t>
+          <t>29616</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>32,23%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>238826</t>
+          <t>239346</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>265469</t>
+          <t>266136</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>68,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>262815</t>
+          <t>263455</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>291306</t>
+          <t>293577</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>69,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>77,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>509365</t>
+          <t>510497</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>549977</t>
+          <t>550379</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>69,91%</t>
+          <t>70,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>75,54%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>83253</t>
+          <t>82586</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>109896</t>
+          <t>109376</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>88560</t>
+          <t>86289</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>117051</t>
+          <t>116411</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>178611</t>
+          <t>178209</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>219223</t>
+          <t>218091</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>29,93%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>89985</t>
+          <t>90510</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>108045</t>
+          <t>107382</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>66,15%</t>
+          <t>66,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>107850</t>
+          <t>107303</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>122609</t>
+          <t>122208</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>76,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>203796</t>
+          <t>202375</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>225769</t>
+          <t>225869</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>73,85%</t>
+          <t>73,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>81,85%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27982</t>
+          <t>28645</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>46042</t>
+          <t>45517</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17321</t>
+          <t>17722</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>32080</t>
+          <t>32627</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>50188</t>
+          <t>50088</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>72161</t>
+          <t>73582</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,66%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>365828</t>
+          <t>367557</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>399645</t>
+          <t>401043</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>69,63%</t>
+          <t>69,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>76,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>415346</t>
+          <t>413730</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>448830</t>
+          <t>448105</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>72,74%</t>
+          <t>72,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>78,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>792992</t>
+          <t>791295</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>837837</t>
+          <t>838073</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>76,42%</t>
+          <t>76,44%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>125745</t>
+          <t>124347</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>159562</t>
+          <t>157833</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>122203</t>
+          <t>122928</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>155687</t>
+          <t>157303</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>258586</t>
+          <t>258350</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>303431</t>
+          <t>305128</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,83%</t>
         </is>
       </c>
     </row>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13259</t>
+          <t>12917</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31848</t>
+          <t>31971</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>58,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18228</t>
+          <t>18923</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31915</t>
+          <t>31690</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>51,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>35307</t>
+          <t>34924</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>58177</t>
+          <t>58390</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>50,04%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22830</t>
+          <t>22707</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>41419</t>
+          <t>41761</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,75%</t>
+          <t>76,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30089</t>
+          <t>30314</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>43776</t>
+          <t>43081</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>48,53%</t>
+          <t>48,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>69,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>58505</t>
+          <t>58292</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>81375</t>
+          <t>81758</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>49,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>70,07%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>113880</t>
+          <t>116463</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>162185</t>
+          <t>160830</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>160975</t>
+          <t>159115</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>210915</t>
+          <t>208033</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>40,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>287961</t>
+          <t>287197</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>355726</t>
+          <t>355078</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,34%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>298325</t>
+          <t>299680</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>346630</t>
+          <t>344047</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64,78%</t>
+          <t>65,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>305704</t>
+          <t>308586</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>355644</t>
+          <t>357504</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>59,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,84%</t>
+          <t>69,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>621403</t>
+          <t>622051</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>689168</t>
+          <t>689932</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,59%</t>
+          <t>63,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>70,61%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26997</t>
+          <t>26604</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44201</t>
+          <t>43747</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33388</t>
+          <t>34566</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>55167</t>
+          <t>56522</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>65845</t>
+          <t>66167</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>93661</t>
+          <t>95250</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>28,61%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>105350</t>
+          <t>105804</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>122554</t>
+          <t>122947</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>70,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>82,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>128182</t>
+          <t>126827</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>149961</t>
+          <t>148783</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,91%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>81,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>239239</t>
+          <t>237650</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>267055</t>
+          <t>266733</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,87%</t>
+          <t>71,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>80,12%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>168438</t>
+          <t>168617</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>220403</t>
+          <t>221455</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>227448</t>
+          <t>224471</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>279996</t>
+          <t>283042</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>412526</t>
+          <t>409681</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>493161</t>
+          <t>484434</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>33,95%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>444335</t>
+          <t>443283</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>496300</t>
+          <t>496121</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,84%</t>
+          <t>66,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>74,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>481976</t>
+          <t>478930</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>534524</t>
+          <t>537501</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,25%</t>
+          <t>62,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,15%</t>
+          <t>70,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>933549</t>
+          <t>942276</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1014184</t>
+          <t>1017029</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>66,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,09%</t>
+          <t>71,28%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P2C_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P2C_R-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>32945</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>26809</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>38402</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>64,13%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>52,19%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>74,75%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>35212</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>29319</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>40755</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>29340</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>41350</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>62,36%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>51,93%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>72,18%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>32945</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>27796</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>38119</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>64,13%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>51,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>73,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>59499</t>
+          <t>59544</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>75975</t>
+          <t>76107</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>55,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>70,58%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>18426</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>12969</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>24562</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>35,87%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>25,25%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>47,81%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>21250</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>15707</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>27143</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>15112</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>27122</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>37,64%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>27,82%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>48,07%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>18426</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>13252</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>23575</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>35,87%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>48,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31858</t>
+          <t>31726</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>48334</t>
+          <t>48289</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>44,78%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>51371</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>51371</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>51371</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>56462</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>56462</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>56462</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>51371</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>51371</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>51371</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>364</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>241812</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>227140</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>255015</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>68,38%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>64,23%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>72,11%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>313</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>208759</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>195061</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>223139</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>195368</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>221388</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>67,27%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>62,86%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>71,91%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>364</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>241812</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>227569</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>255192</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>68,38%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>64,35%</t>
+          <t>62,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>72,16%</t>
+          <t>71,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>432589</t>
+          <t>429489</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>469943</t>
+          <t>468511</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>65,15%</t>
+          <t>64,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>70,78%</t>
+          <t>70,56%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>111824</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>98621</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>126496</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>31,62%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>27,89%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>35,77%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>101558</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>87178</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>115256</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>88929</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>114949</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>32,73%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>28,09%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>37,14%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>111824</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>98444</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>126067</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>31,62%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>194010</t>
+          <t>195442</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>231364</t>
+          <t>234464</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>35,31%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>532</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>353636</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>353636</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>353636</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>465</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>310317</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>310317</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>310317</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>532</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>353636</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>353636</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>353636</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>89064</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>81569</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>96441</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>72,09%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>66,03%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>78,06%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>155</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>106760</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>98249</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>113989</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>98405</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>113973</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>78,17%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>71,93%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>83,46%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>89064</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>80473</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>97282</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>72,09%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>72,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>78,74%</t>
+          <t>83,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>183495</t>
+          <t>184433</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>206613</t>
+          <t>206742</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>70,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>79,48%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>34478</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>27101</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>41973</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>27,91%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>21,94%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>33,97%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>29821</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>22592</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>38332</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>22608</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>38176</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>21,83%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>16,54%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>28,07%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>34478</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>26260</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>43069</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>27,91%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>53510</t>
+          <t>53381</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>76628</t>
+          <t>75690</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,1%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>123542</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>123542</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>123542</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>198</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>136581</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>136581</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>136581</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>123542</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>123542</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>123542</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>545</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>363821</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>345138</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>379567</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>68,83%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>65,3%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>71,81%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>520</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>350731</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>334656</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>367316</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>333008</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>365889</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>69,68%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>66,48%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>72,97%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>545</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>363821</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>346730</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>380608</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>68,83%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>66,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>72,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>689538</t>
+          <t>692115</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>738597</t>
+          <t>737936</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>66,82%</t>
+          <t>67,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>71,58%</t>
+          <t>71,51%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>164728</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>148982</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>183411</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>31,17%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>28,19%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>34,7%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>152628</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>136043</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>168703</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>137470</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>170351</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>30,32%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>27,03%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>33,52%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>247</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>164728</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>147941</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>181819</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>31,17%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>293311</t>
+          <t>293972</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>342370</t>
+          <t>339793</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>32,93%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>746</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>503359</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>503359</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>503359</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>792</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +2158,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2326,72 +2326,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>53810</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>48987</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>57557</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>86,66%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>78,9%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>92,7%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>47890</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>42741</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>51472</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>42657</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>51717</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>86,31%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>77,03%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>92,77%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>53810</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>48848</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>57583</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>86,66%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>78,67%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>94912</t>
+          <t>94349</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>107615</t>
+          <t>107323</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>80,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,28%</t>
         </is>
       </c>
     </row>
@@ -2439,72 +2439,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>8280</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4533</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>13103</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>13,34%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>7,3%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>21,1%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>7594</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>4012</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>12743</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>3767</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>12827</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>13,69%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>7,23%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>22,97%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>8280</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>4507</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>13242</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>13,34%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9959</t>
+          <t>10251</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>22662</t>
+          <t>23225</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,75%</t>
         </is>
       </c>
     </row>
@@ -2552,57 +2552,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>62090</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>62090</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>62090</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>55484</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>55484</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>55484</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>62090</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>62090</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>62090</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>418</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>291627</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>280583</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>301018</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>85,82%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>82,57%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>88,59%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>393</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>271554</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>262695</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>279880</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>262031</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>280065</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>89,14%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>86,23%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>91,87%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>418</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>291627</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>280295</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>301359</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>85,82%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>550182</t>
+          <t>546809</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>576720</t>
+          <t>575635</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,32%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>48166</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>38775</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>59210</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>14,18%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>11,41%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>17,43%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>33099</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>24773</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>41958</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>24588</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>42622</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>10,86%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>8,13%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>13,77%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>48166</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>38434</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>59498</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>14,18%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>67726</t>
+          <t>68811</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>94264</t>
+          <t>97637</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>15,15%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>339793</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>339793</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>339793</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>441</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>304653</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>304653</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>304653</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>487</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>339793</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>339793</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>339793</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>128208</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>122293</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>132044</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>93,65%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>89,33%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>96,45%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>155</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>109494</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>104652</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>113071</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>104076</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>112868</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>93,72%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>89,58%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>96,78%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>128208</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>123058</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>131854</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>93,65%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>230908</t>
+          <t>230082</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>243142</t>
+          <t>243034</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,79%</t>
         </is>
       </c>
     </row>
@@ -3125,72 +3125,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>8690</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4854</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>14605</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>6,35%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>3,55%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>10,67%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>7333</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>3756</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>12175</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>3959</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>12751</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>6,28%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>3,22%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>10,42%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>8690</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>5044</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>13840</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>6,35%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>10583</t>
+          <t>10691</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>22817</t>
+          <t>23643</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,32%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>136898</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>136898</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>136898</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>166</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>116827</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>116827</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>116827</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>193</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>136898</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>136898</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>136898</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>473645</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>460235</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>484394</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>87,91%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>85,42%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>89,91%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>617</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>428939</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>418324</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>438557</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>416621</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>438190</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>89,93%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>87,71%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>91,95%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>675</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>473645</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>461494</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>486339</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>87,91%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>884572</t>
+          <t>886523</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>918467</t>
+          <t>919393</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,51%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>65136</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>54387</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>78546</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>12,09%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>10,09%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>14,58%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>48026</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>38408</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>58641</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>38775</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>60344</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>10,07%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>8,05%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>12,29%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>65136</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>52442</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>77287</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>12,09%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>97279</t>
+          <t>96353</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>131174</t>
+          <t>129223</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,72%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>769</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>687</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>476965</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>476965</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>476965</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>769</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +3761,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3929,72 +3929,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>38672</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>32678</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>42831</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>75,48%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>63,78%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>83,59%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>31130</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>26105</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>34829</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>26364</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>35041</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>76,6%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>64,23%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>85,7%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>38672</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>32882</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>43438</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>75,48%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>64,18%</t>
+          <t>64,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>62262</t>
+          <t>62749</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>76064</t>
+          <t>75682</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>68,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>82,37%</t>
         </is>
       </c>
     </row>
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>12565</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>8406</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>18559</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>24,52%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>16,41%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>36,22%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>9511</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>5812</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>14536</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>5600</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>14277</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>23,4%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>14,3%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>35,77%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>12565</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>7799</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>18355</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>24,52%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15814</t>
+          <t>16196</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>29616</t>
+          <t>29129</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>31,7%</t>
         </is>
       </c>
     </row>
@@ -4155,57 +4155,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>51237</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>51237</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>51237</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>40641</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>40641</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>40641</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>51237</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>51237</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>51237</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4272,72 +4272,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>277379</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>261333</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>291591</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>73,02%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>68,8%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>76,76%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>389</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>252940</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>239346</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>266136</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>239129</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>265944</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>72,53%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>68,64%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>76,32%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>404</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>277379</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>263455</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>293577</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>73,02%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>69,35%</t>
+          <t>68,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>77,28%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>510497</t>
+          <t>507901</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>550379</t>
+          <t>547873</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>70,07%</t>
+          <t>69,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>75,54%</t>
+          <t>75,2%</t>
         </is>
       </c>
     </row>
@@ -4385,72 +4385,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>102487</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>88275</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>118533</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>26,98%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>23,24%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>31,2%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>95782</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>82586</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>109376</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>82778</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>109593</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>27,47%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>23,68%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>31,36%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>102487</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>86289</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>116411</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>26,98%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>178209</t>
+          <t>180715</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>218091</t>
+          <t>220687</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>30,29%</t>
         </is>
       </c>
     </row>
@@ -4498,57 +4498,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>544</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>379866</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>379866</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>379866</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>525</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>348722</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>348722</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>348722</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>544</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>379866</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>379866</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>379866</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4615,72 +4615,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>115798</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>107181</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>122158</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>82,75%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>76,6%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>87,3%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>151</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>99573</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>90510</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>107382</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>91326</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>108533</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>73,2%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>66,54%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>78,94%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>115798</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>107303</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>122208</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>82,75%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>76,68%</t>
+          <t>67,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>79,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>202375</t>
+          <t>203643</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>225869</t>
+          <t>226107</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>73,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>81,94%</t>
         </is>
       </c>
     </row>
@@ -4728,72 +4728,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>24132</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>17772</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>32749</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>17,25%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>12,7%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>23,4%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>36454</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>28645</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>45517</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>27494</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>44701</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>26,8%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>21,06%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>33,46%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>24132</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>17722</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>32627</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>17,25%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>50088</t>
+          <t>49850</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>73582</t>
+          <t>72314</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,2%</t>
         </is>
       </c>
     </row>
@@ -4841,57 +4841,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>139930</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>139930</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>139930</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>202</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>136027</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>136027</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>136027</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>139930</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>139930</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>139930</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4958,72 +4958,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>431850</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>415584</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>449887</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>75,63%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>72,78%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>78,78%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>589</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>383642</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>367557</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>401043</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>366597</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>400140</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>73,02%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>69,96%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>76,33%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>632</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>431850</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>413730</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>448105</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>75,63%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>69,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>76,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>791295</t>
+          <t>791620</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>838073</t>
+          <t>840951</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>72,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>76,44%</t>
+          <t>76,7%</t>
         </is>
       </c>
     </row>
@@ -5071,72 +5071,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>139183</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>121146</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>155449</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>24,37%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>21,22%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>27,22%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>201</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>141748</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>124347</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>157833</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>125250</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>158793</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>26,98%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>23,67%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>30,04%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>193</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>139183</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>122928</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>157303</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>24,37%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>258350</t>
+          <t>255472</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>305128</t>
+          <t>304803</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,8%</t>
         </is>
       </c>
     </row>
@@ -5184,57 +5184,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>825</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>790</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>525390</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>525390</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>525390</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>825</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +5364,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5532,72 +5532,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>23275</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>16759</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>29496</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>41,03%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>29,54%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>51,99%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>20399</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>12917</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>31971</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>37,31%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>23,62%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>58,47%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>24782</t>
+          <t>16494</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18923</t>
+          <t>11385</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31690</t>
+          <t>22440</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,11%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>45181</t>
+          <t>39769</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34924</t>
+          <t>31962</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>58390</t>
+          <t>49257</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,04%</t>
+          <t>47,6%</t>
         </is>
       </c>
     </row>
@@ -5645,72 +5645,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>33457</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>27236</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>39973</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>58,97%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>48,01%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>70,46%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>34279</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>22707</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>41761</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>62,69%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>41,53%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>76,38%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>37222</t>
+          <t>30264</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30314</t>
+          <t>24318</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>43081</t>
+          <t>35373</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>60,03%</t>
+          <t>64,72%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>48,89%</t>
+          <t>52,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,48%</t>
+          <t>75,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>71501</t>
+          <t>63721</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>58292</t>
+          <t>54233</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>81758</t>
+          <t>71528</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>61,57%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>52,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,07%</t>
+          <t>69,12%</t>
         </is>
       </c>
     </row>
@@ -5758,57 +5758,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5875,72 +5875,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>171682</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>152198</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>194793</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>36,09%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>32,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>40,95%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>213</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>142281</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>116463</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>160830</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>30,9%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>25,29%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>34,92%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>181850</t>
+          <t>143892</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>159115</t>
+          <t>128585</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>208033</t>
+          <t>160880</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>324131</t>
+          <t>315574</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>287197</t>
+          <t>288682</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>355078</t>
+          <t>345279</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>34,75%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>38,02%</t>
         </is>
       </c>
     </row>
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>410</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>303996</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>280885</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>323480</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>63,91%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>59,05%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>68,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>430</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>318229</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>299680</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>344047</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>69,1%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>65,08%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>74,71%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>410</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>334769</t>
+          <t>288556</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>308586</t>
+          <t>271568</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>357504</t>
+          <t>303863</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>64,8%</t>
+          <t>66,73%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,73%</t>
+          <t>62,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>70,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>652998</t>
+          <t>592552</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>622051</t>
+          <t>562847</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>689932</t>
+          <t>619444</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>66,83%</t>
+          <t>65,25%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,66%</t>
+          <t>61,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>68,21%</t>
         </is>
       </c>
     </row>
@@ -6101,57 +6101,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>643</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>432448</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>432448</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>432448</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>977129</t>
+          <t>908126</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>977129</t>
+          <t>908126</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>977129</t>
+          <t>908126</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6218,72 +6218,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>42410</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>32526</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>53004</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>25,18%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>19,31%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>31,47%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>35113</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>26604</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>43747</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>23,48%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>17,79%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>29,25%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>44413</t>
+          <t>34595</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34566</t>
+          <t>25487</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>56522</t>
+          <t>42874</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>79526</t>
+          <t>77005</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>66167</t>
+          <t>63488</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>95250</t>
+          <t>90645</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,47%</t>
         </is>
       </c>
     </row>
@@ -6331,72 +6331,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>126009</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>115415</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>135893</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>74,82%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>68,53%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>80,69%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>175</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>114438</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>105804</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>122947</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>76,52%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>70,75%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>82,21%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>138936</t>
+          <t>115381</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>126827</t>
+          <t>107102</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>148783</t>
+          <t>124489</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>76,93%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>71,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>83,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>253374</t>
+          <t>241390</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>237650</t>
+          <t>227750</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>266733</t>
+          <t>254907</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>75,81%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,39%</t>
+          <t>71,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,12%</t>
+          <t>80,06%</t>
         </is>
       </c>
     </row>
@@ -6444,57 +6444,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>332900</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6561,72 +6561,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>237366</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>214504</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>264437</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>33,87%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>30,61%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>37,73%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>295</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>197792</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>168617</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>221455</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>29,75%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>25,37%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>33,31%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>341</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>251045</t>
+          <t>194981</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>224471</t>
+          <t>174847</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>283042</t>
+          <t>216012</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>448837</t>
+          <t>432348</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>409681</t>
+          <t>403790</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>484434</t>
+          <t>464139</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>34,9%</t>
         </is>
       </c>
     </row>
@@ -6674,72 +6674,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>463463</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>436392</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>486325</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>66,13%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>62,27%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>69,39%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>647</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>466946</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>443283</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>496121</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>70,25%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>66,69%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>74,63%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>636</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>510927</t>
+          <t>434201</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>478930</t>
+          <t>413170</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>537501</t>
+          <t>454335</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>69,01%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
+          <t>65,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>72,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>977873</t>
+          <t>897663</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>942276</t>
+          <t>865872</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1017029</t>
+          <t>926221</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>67,49%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,05%</t>
+          <t>65,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>69,64%</t>
         </is>
       </c>
     </row>
@@ -6787,57 +6787,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>942</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>664738</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>664738</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>664738</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>977</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629182</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629182</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629182</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1426710</t>
+          <t>1330011</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1426710</t>
+          <t>1330011</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1426710</t>
+          <t>1330011</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
